--- a/testakten/versausgleich-haerte-bgh-schaefer-nuernberg/xlsx/versorgungsausgleich_berechnung_schaefer.xlsx
+++ b/testakten/versausgleich-haerte-bgh-schaefer-nuernberg/xlsx/versorgungsausgleich_berechnung_schaefer.xlsx
@@ -501,21 +501,22 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Versorgungsausgleichsberechnung Schaefer ./. Schaefer</t>
+          <t>Versorgungsausgleichsberechnung Schäfer ./. Schäfer</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Az. AG Nuernberg-Fuerth 110 F 2418/21 ; Ehezeit 01.09.1987 - 30.04.2021</t>
-        </is>
-      </c>
-    </row>
+          <t>Az. AG Nürnberg-Fürth 110 F 2418/21 ; Ehezeit 01.09.1987 - 30.04.2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Versorgungstraeger / Vertrag</t>
+          <t>Versorgungsträger / Vertrag</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -547,12 +548,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Bayerische Aerzteversorgung (Mitgl-Nr. 14-072 184/1958)</t>
+          <t>Bayerische Ärzteversorgung (Mitgl-Nr. 14-072 184/1958)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Dr. M. Schaefer</t>
+          <t>Dr. M. Schäfer</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -570,7 +571,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>interne Teilung § 10</t>
+          <t>interne Teilung Paragraf 10</t>
         </is>
       </c>
     </row>
@@ -582,7 +583,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Dr. M. Schaefer</t>
+          <t>Dr. M. Schäfer</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -600,7 +601,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>interne Teilung § 10</t>
+          <t>interne Teilung Paragraf 10</t>
         </is>
       </c>
     </row>
@@ -612,7 +613,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Dr. M. Schaefer</t>
+          <t>Dr. M. Schäfer</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -630,19 +631,19 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>externe Teilung § 14</t>
+          <t>externe Teilung Paragraf 14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Wuerttembergische Direktvers (4471 9982 73)</t>
+          <t>Württembergische Direktvers (4471 9982 73)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Dr. M. Schaefer</t>
+          <t>Dr. M. Schäfer</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -660,7 +661,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>externe Teilung § 14</t>
+          <t>externe Teilung Paragraf 14</t>
         </is>
       </c>
     </row>
@@ -672,7 +673,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Frau L. Schaefer</t>
+          <t>Frau L. Schäfer</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -690,7 +691,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>interne Teilung § 10</t>
+          <t>interne Teilung Paragraf 10</t>
         </is>
       </c>
     </row>
@@ -702,7 +703,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Frau L. Schaefer</t>
+          <t>Frau L. Schäfer</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -720,21 +721,23 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>interne Teilung § 10</t>
-        </is>
-      </c>
-    </row>
+          <t>interne Teilung Paragraf 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Saldenuebersicht (informativ)</t>
-        </is>
-      </c>
-    </row>
+          <t>Saldenübersicht (informativ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ausgleichssumme (Kapital), Anteile Dr. M. Schaefer:</t>
+          <t>Ausgleichssumme (Kapital), Anteile Dr. M. Schäfer:</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -744,24 +747,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ausgleichssumme (Kapital), Anteile Frau L. Schaefer:</t>
+          <t>Ausgleichssumme (Kapital), Anteile Frau L. Schäfer:</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
         <v>112559</v>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Bei Ausschluss nach § 27 VersAusglG</t>
+          <t>Bei Ausschluss nach Paragraf 27 VersAusglG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Beide Anrechte bleiben in voller Hoehe beim urspruenglichen Inhaber.</t>
+          <t>Beide Anrechte bleiben in voller Höhe beim ursprünglichen Inhaber.</t>
         </is>
       </c>
     </row>
@@ -797,6 +801,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -810,7 +815,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Empfaenger nach VA EUR/M</t>
+          <t>Empfänger nach VA EUR/M</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -827,7 +832,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Bayerische Aerzteversorgung</t>
+          <t>Bayerische Ärzteversorgung</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
@@ -900,6 +905,7 @@
         <v>-90.01000000000001</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -913,6 +919,7 @@
         <v>1086.52</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
@@ -923,21 +930,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Negative Werte bedeuten Reduktion bei Dr. M. Schaefer.</t>
+          <t>Negative Werte bedeuten Reduktion bei Dr. M. Schäfer.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Positive Werte bei Frau L. Schaefer bedeuten Zugewinn an Anwartschaft.</t>
-        </is>
-      </c>
-    </row>
+          <t>Positive Werte bei Frau L. Schäfer bedeuten Zugewinn an Anwartschaft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Wenn § 27 VersAusglG angewendet wird, entfaellt diese Tabelle (kein VA).</t>
+          <t>Wenn Paragraf 27 VersAusglG angewendet wird, entfällt diese Tabelle (kein VA).</t>
         </is>
       </c>
     </row>
